--- a/mobile/assets/templates/kuru_tip_hybrid.xlsx
+++ b/mobile/assets/templates/kuru_tip_hybrid.xlsx
@@ -8559,8 +8559,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -8578,8 +8578,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="B16:B19"/>
-    <mergeCell ref="D26:E26"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>
@@ -8686,7 +8686,8 @@
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -11611,7 +11612,8 @@
     <mergeCell ref="O17:S17"/>
     <mergeCell ref="O11:S11"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -13073,7 +13075,8 @@
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="I40:J40"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -14397,8 +14400,8 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F25:I25"/>
+    <mergeCell ref="N39:O39"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="N39:O39"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="J28:M28"/>
@@ -14514,7 +14517,8 @@
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="N36:O36"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -16045,8 +16049,8 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="I27:I28"/>
     <mergeCell ref="W38:AJ38"/>
-    <mergeCell ref="I27:I28"/>
     <mergeCell ref="J23:Q23"/>
     <mergeCell ref="W28:AD28"/>
     <mergeCell ref="N19:Q19"/>
@@ -16067,7 +16071,8 @@
     <mergeCell ref="W42:AJ42"/>
     <mergeCell ref="K2:Q2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -17563,7 +17568,8 @@
     <mergeCell ref="O30:Q30"/>
     <mergeCell ref="B13:Q13"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -18811,7 +18817,8 @@
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -29810,7 +29817,8 @@
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -31365,8 +31373,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -31384,8 +31392,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="B16:B19"/>
-    <mergeCell ref="D26:E26"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>
@@ -31492,7 +31500,8 @@
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mobile/assets/templates/kuru_tip_hybrid.xlsx
+++ b/mobile/assets/templates/kuru_tip_hybrid.xlsx
@@ -8559,8 +8559,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -8578,8 +8578,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B16:B19"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>
@@ -14400,8 +14400,8 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B8:I8"/>
     <mergeCell ref="N39:O39"/>
-    <mergeCell ref="B8:I8"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="J28:M28"/>
@@ -16049,8 +16049,8 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="I27:I28"/>
-    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="J23:Q23"/>
     <mergeCell ref="W28:AD28"/>
     <mergeCell ref="N19:Q19"/>
@@ -31373,8 +31373,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -31392,8 +31392,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B16:B19"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>

--- a/mobile/assets/templates/kuru_tip_hybrid.xlsx
+++ b/mobile/assets/templates/kuru_tip_hybrid.xlsx
@@ -2916,7 +2916,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3069,7 +3069,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3114,7 +3114,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3354,7 +3354,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3507,7 +3507,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3552,7 +3552,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3632,7 +3632,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3701,7 +3701,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3793,7 +3793,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3911,7 +3911,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3994,7 +3994,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4063,7 +4063,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4155,7 +4155,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4273,7 +4273,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4363,7 +4363,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4436,7 +4436,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4528,7 +4528,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4646,7 +4646,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4729,7 +4729,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4826,7 +4826,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4938,7 +4938,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5000,7 +5000,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5039,7 +5039,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6670,25 +6670,11 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
-    <row r="43"/>
     <row r="44" s="227"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>
@@ -28741,7 +28727,7 @@
       </c>
       <c r="C16" s="482" t="n"/>
       <c r="D16" s="517" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="482" t="n"/>
       <c r="F16" s="518" t="inlineStr">
@@ -28998,7 +28984,7 @@
       </c>
       <c r="E26" s="99" t="n"/>
       <c r="F26" s="527" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="528" t="inlineStr">
         <is>
@@ -29055,7 +29041,7 @@
       </c>
       <c r="E27" s="99" t="n"/>
       <c r="F27" s="527" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="528" t="inlineStr">
         <is>
@@ -29112,7 +29098,7 @@
       </c>
       <c r="E28" s="99" t="n"/>
       <c r="F28" s="527" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="528" t="inlineStr">
         <is>
@@ -29169,7 +29155,7 @@
       </c>
       <c r="E29" s="99" t="n"/>
       <c r="F29" s="527" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="528" t="inlineStr">
         <is>

--- a/mobile/assets/templates/kuru_tip_hybrid.xlsx
+++ b/mobile/assets/templates/kuru_tip_hybrid.xlsx
@@ -2916,7 +2916,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3069,7 +3069,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3114,7 +3114,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3354,7 +3354,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3507,7 +3507,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3552,7 +3552,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3632,7 +3632,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3701,7 +3701,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3793,7 +3793,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3911,7 +3911,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3994,7 +3994,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4063,7 +4063,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4155,7 +4155,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4273,7 +4273,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4363,7 +4363,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4436,7 +4436,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4528,7 +4528,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4646,7 +4646,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4729,7 +4729,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4826,7 +4826,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4938,7 +4938,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5000,7 +5000,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5039,7 +5039,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6670,11 +6670,25 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
+    <row r="43"/>
     <row r="44" s="227"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>
@@ -19581,7 +19595,7 @@
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="280" t="inlineStr">
         <is>
-          <t>Yağ Seviyesi Kontrolü</t>
+          <t>Fan ON</t>
         </is>
       </c>
       <c r="F29" s="89" t="inlineStr">
@@ -19717,7 +19731,7 @@
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="280" t="inlineStr">
         <is>
-          <t>Basınç Açma</t>
+          <t>Termometre Alarm</t>
         </is>
       </c>
       <c r="F33" s="89" t="inlineStr">
@@ -19739,7 +19753,7 @@
       <c r="J33" s="93" t="n"/>
       <c r="K33" s="280" t="inlineStr">
         <is>
-          <t>Yağ Kaçağı Kontrolü</t>
+          <t>Epoksi Kontrolü</t>
         </is>
       </c>
       <c r="O33" s="116" t="inlineStr">
@@ -19787,7 +19801,7 @@
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="280" t="inlineStr">
         <is>
-          <t>Gaz Açma</t>
+          <t>Termometre Trip</t>
         </is>
       </c>
       <c r="F35" s="89" t="inlineStr">
@@ -19809,7 +19823,7 @@
       <c r="J35" s="93" t="n"/>
       <c r="K35" s="280" t="inlineStr">
         <is>
-          <t>Kademe Conta Kontrolü</t>
+          <t>Termistor Kontrolü</t>
         </is>
       </c>
       <c r="O35" s="89" t="inlineStr">
@@ -19857,7 +19871,7 @@
       <c r="A37" s="10" t="n"/>
       <c r="B37" s="280" t="inlineStr">
         <is>
-          <t>Termik Alarm</t>
+          <t>Fan OFF</t>
         </is>
       </c>
       <c r="F37" s="110" t="inlineStr">
@@ -19879,7 +19893,7 @@
       <c r="J37" s="93" t="n"/>
       <c r="K37" s="247" t="inlineStr">
         <is>
-          <t>O.G Conta Kontrolü</t>
+          <t>Topraklama Bağlantısı</t>
         </is>
       </c>
       <c r="O37" s="111" t="inlineStr">
@@ -19925,11 +19939,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" s="227">
       <c r="A39" s="10" t="n"/>
-      <c r="B39" s="280" t="inlineStr">
-        <is>
-          <t>Termik Açma</t>
-        </is>
-      </c>
+      <c r="B39" s="280" t="n"/>
       <c r="F39" s="89" t="inlineStr">
         <is>
           <t>:</t>
@@ -19941,17 +19951,9 @@
         </is>
       </c>
       <c r="H39" s="487" t="n"/>
-      <c r="I39" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="I39" s="93" t="n"/>
       <c r="J39" s="93" t="n"/>
-      <c r="K39" s="291" t="inlineStr">
-        <is>
-          <t>Kapak Conta Kontrolü</t>
-        </is>
-      </c>
+      <c r="K39" s="291" t="n"/>
       <c r="O39" s="89" t="inlineStr">
         <is>
           <t>:</t>
@@ -19963,11 +19965,7 @@
         </is>
       </c>
       <c r="Q39" s="487" t="n"/>
-      <c r="R39" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="R39" s="93" t="n"/>
       <c r="S39" s="93" t="n"/>
       <c r="T39" s="11" t="n"/>
     </row>
@@ -19995,11 +19993,7 @@
     </row>
     <row r="41">
       <c r="A41" s="10" t="n"/>
-      <c r="B41" s="247" t="inlineStr">
-        <is>
-          <t>İzolatör Kontrolü</t>
-        </is>
-      </c>
+      <c r="B41" s="247" t="n"/>
       <c r="F41" s="89" t="inlineStr">
         <is>
           <t>:</t>
@@ -20011,17 +20005,9 @@
         </is>
       </c>
       <c r="H41" s="487" t="n"/>
-      <c r="I41" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="I41" s="93" t="n"/>
       <c r="J41" s="93" t="n"/>
-      <c r="K41" s="248" t="inlineStr">
-        <is>
-          <t>A.G Conta Kontrolü</t>
-        </is>
-      </c>
+      <c r="K41" s="248" t="n"/>
       <c r="O41" s="89" t="inlineStr">
         <is>
           <t>:</t>
@@ -20033,11 +20019,7 @@
         </is>
       </c>
       <c r="Q41" s="487" t="n"/>
-      <c r="R41" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="R41" s="93" t="n"/>
       <c r="S41" s="93" t="n"/>
       <c r="T41" s="11" t="n"/>
     </row>

--- a/mobile/assets/templates/kuru_tip_hybrid.xlsx
+++ b/mobile/assets/templates/kuru_tip_hybrid.xlsx
@@ -2916,7 +2916,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3069,7 +3069,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3114,7 +3114,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3354,7 +3354,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3507,7 +3507,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3552,7 +3552,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3632,7 +3632,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3701,7 +3701,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3793,7 +3793,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3911,7 +3911,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3994,7 +3994,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4063,7 +4063,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4155,7 +4155,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4273,7 +4273,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4363,7 +4363,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4436,7 +4436,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4528,7 +4528,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4646,7 +4646,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4729,7 +4729,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4826,7 +4826,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4938,7 +4938,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5000,7 +5000,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5039,7 +5039,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6670,25 +6670,11 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
-    <row r="43"/>
     <row r="44" s="227"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>
@@ -20048,29 +20034,10 @@
     <row r="43" ht="3" customHeight="1" s="227">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="485" t="n"/>
-      <c r="C43" s="47" t="n"/>
-      <c r="D43" s="47" t="n"/>
-      <c r="E43" s="47" t="n"/>
-      <c r="F43" s="47" t="n"/>
-      <c r="G43" s="47" t="n"/>
-      <c r="H43" s="47" t="n"/>
-      <c r="I43" s="47" t="n"/>
-      <c r="J43" s="47" t="n"/>
-      <c r="K43" s="47" t="n"/>
-      <c r="L43" s="47" t="n"/>
-      <c r="M43" s="47" t="n"/>
-      <c r="N43" s="47" t="n"/>
-      <c r="O43" s="47" t="n"/>
-      <c r="P43" s="47" t="n"/>
-      <c r="Q43" s="47" t="n"/>
-      <c r="R43" s="47" t="n"/>
-      <c r="S43" s="211" t="n"/>
       <c r="T43" s="11" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="227">
       <c r="A44" s="10" t="n"/>
-      <c r="B44" s="62" t="n"/>
-      <c r="S44" s="212" t="n"/>
       <c r="T44" s="11" t="n"/>
       <c r="V44" s="485" t="inlineStr">
         <is>
@@ -20101,8 +20068,6 @@
     </row>
     <row r="45" ht="3" customHeight="1" s="227">
       <c r="A45" s="10" t="n"/>
-      <c r="B45" s="62" t="n"/>
-      <c r="S45" s="212" t="n"/>
       <c r="T45" s="11" t="n"/>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="127" t="n"/>
@@ -20125,8 +20090,6 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
-      <c r="B46" s="62" t="n"/>
-      <c r="S46" s="212" t="n"/>
       <c r="T46" s="11" t="n"/>
       <c r="V46" s="489" t="inlineStr">
         <is>
@@ -20173,8 +20136,6 @@
     </row>
     <row r="47" ht="3" customHeight="1" s="227">
       <c r="A47" s="10" t="n"/>
-      <c r="B47" s="62" t="n"/>
-      <c r="S47" s="212" t="n"/>
       <c r="T47" s="11" t="n"/>
       <c r="V47" s="3" t="n"/>
       <c r="W47" s="127" t="n"/>
@@ -20197,8 +20158,6 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
-      <c r="B48" s="62" t="n"/>
-      <c r="S48" s="212" t="n"/>
       <c r="T48" s="11" t="n"/>
       <c r="V48" s="490">
         <f>V57/1.0525889</f>
@@ -20239,8 +20198,6 @@
     </row>
     <row r="49" ht="3" customHeight="1" s="227">
       <c r="A49" s="10" t="n"/>
-      <c r="B49" s="62" t="n"/>
-      <c r="S49" s="212" t="n"/>
       <c r="T49" s="11" t="n"/>
       <c r="V49" s="42" t="n"/>
       <c r="W49" s="43" t="n"/>
@@ -20263,8 +20220,6 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
-      <c r="B50" s="62" t="n"/>
-      <c r="S50" s="212" t="n"/>
       <c r="T50" s="11" t="n"/>
       <c r="V50" s="328" t="inlineStr">
         <is>
@@ -20311,24 +20266,6 @@
     </row>
     <row r="51" ht="3" customHeight="1" s="227">
       <c r="A51" s="10" t="n"/>
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="50" t="n"/>
-      <c r="D51" s="50" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="50" t="n"/>
-      <c r="H51" s="50" t="n"/>
-      <c r="I51" s="50" t="n"/>
-      <c r="J51" s="50" t="n"/>
-      <c r="K51" s="50" t="n"/>
-      <c r="L51" s="50" t="n"/>
-      <c r="M51" s="50" t="n"/>
-      <c r="N51" s="50" t="n"/>
-      <c r="O51" s="50" t="n"/>
-      <c r="P51" s="50" t="n"/>
-      <c r="Q51" s="50" t="n"/>
-      <c r="R51" s="50" t="n"/>
-      <c r="S51" s="213" t="n"/>
       <c r="T51" s="11" t="n"/>
     </row>
     <row r="52" ht="3" customHeight="1" s="227">
@@ -21563,7 +21500,7 @@
       <c r="T83" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="161">
+  <mergeCells count="160">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="F68:G68"/>
     <mergeCell ref="AL57:AN57"/>
@@ -21575,7 +21512,6 @@
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="K5:S6"/>
     <mergeCell ref="V66:X66"/>
-    <mergeCell ref="B43:S51"/>
     <mergeCell ref="K17:M17"/>
     <mergeCell ref="I66:J66"/>
     <mergeCell ref="K33:N33"/>
